--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04 14:10</t>
+    <t xml:space="preserve">2026-08-07 06:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 06:37</t>
+    <t xml:space="preserve">2026-08-13 13:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13 13:02</t>
+    <t xml:space="preserve">2026-08-19 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:05</t>
+    <t xml:space="preserve">2026-08-28 11:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:12</t>
+    <t xml:space="preserve">2026-09-01 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 11:38</t>
+    <t xml:space="preserve">2026-09-04 20:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 20:12</t>
+    <t xml:space="preserve">2026-09-06 16:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
